--- a/docs/video_manual/v1.6/exports/Report_Local_Auto_Trips.xlsx
+++ b/docs/video_manual/v1.6/exports/Report_Local_Auto_Trips.xlsx
@@ -479,7 +479,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Tulsyan (Demonstration) · 01-10-2026 to … (Dispatch date) · generated 18-10-2026 00:47 by Master Administrator</t>
+          <t>Tulsyan (Demonstration) · 01-10-2026 to … (Dispatch date) · generated 21-10-2026 05:16 by Master Administrator</t>
         </is>
       </c>
     </row>
@@ -547,7 +547,7 @@
     </row>
     <row r="5">
       <c r="A5" s="4" t="n">
-        <v>46313</v>
+        <v>46316</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>30</v>
       </c>
       <c r="H5" s="6" t="n">
-        <v>500.01</v>
+        <v>500</v>
       </c>
       <c r="I5" s="6" t="n">
-        <v>500.01</v>
+        <v>500</v>
       </c>
       <c r="J5" s="6" t="n">
         <v>16.67</v>
       </c>
       <c r="K5" s="6" t="n">
-        <v>500.01</v>
+        <v>500</v>
       </c>
       <c r="L5" t="inlineStr">
         <is>
@@ -595,7 +595,7 @@
     </row>
     <row r="6">
       <c r="A6" s="4" t="n">
-        <v>46313</v>
+        <v>46316</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
@@ -643,7 +643,7 @@
     </row>
     <row r="7">
       <c r="A7" s="4" t="n">
-        <v>46313</v>
+        <v>46316</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>10</v>
       </c>
       <c r="H7" s="6" t="n">
-        <v>600.01</v>
+        <v>550</v>
       </c>
       <c r="I7" s="6" t="n">
-        <v>600.01</v>
+        <v>550</v>
       </c>
       <c r="J7" s="6" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="K7" s="6" t="n">
-        <v>600.01</v>
+        <v>550</v>
       </c>
       <c r="L7" t="inlineStr">
         <is>
@@ -706,16 +706,16 @@
         <v>61</v>
       </c>
       <c r="H8" s="10" t="n">
-        <v>1532.02</v>
+        <v>1482</v>
       </c>
       <c r="I8" s="10" t="n">
-        <v>1532.02</v>
+        <v>1482</v>
       </c>
       <c r="J8" s="10" t="n">
-        <v>25.12</v>
+        <v>24.3</v>
       </c>
       <c r="K8" s="10" t="n">
-        <v>1532.02</v>
+        <v>1482</v>
       </c>
       <c r="L8" s="8" t="n"/>
     </row>

--- a/docs/video_manual/v1.6/exports/Report_Local_Auto_Trips.xlsx
+++ b/docs/video_manual/v1.6/exports/Report_Local_Auto_Trips.xlsx
@@ -22,7 +22,7 @@
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd"/>
     <numFmt numFmtId="165" formatCode="dd-mm-yyyy"/>
   </numFmts>
-  <fonts count="5">
+  <fonts count="6">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -39,6 +39,11 @@
       <i val="1"/>
       <color rgb="005B6675"/>
       <sz val="9"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00B45309"/>
+      <sz val="12"/>
     </font>
     <font>
       <b val="1"/>
@@ -73,20 +78,21 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="4" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="165" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="3" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="4" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="3" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="4" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -479,74 +485,77 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Tulsyan (Demonstration) · 01-10-2026 to … (Dispatch date) · generated 21-10-2026 05:16 by Master Administrator</t>
-        </is>
-      </c>
+          <t>Tulsyan (Demonstration) · 01-10-2026 to … (Dispatch date) · generated 21-10-2026 14:47 by Master Administrator</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="3" t="n"/>
     </row>
     <row r="4">
-      <c r="A4" s="3" t="inlineStr">
+      <c r="A4" s="4" t="inlineStr">
         <is>
           <t>Date</t>
         </is>
       </c>
-      <c r="B4" s="3" t="inlineStr">
+      <c r="B4" s="4" t="inlineStr">
         <is>
           <t>Gatepass</t>
         </is>
       </c>
-      <c r="C4" s="3" t="inlineStr">
+      <c r="C4" s="4" t="inlineStr">
         <is>
           <t>Depot</t>
         </is>
       </c>
-      <c r="D4" s="3" t="inlineStr">
+      <c r="D4" s="4" t="inlineStr">
         <is>
           <t>Local auto</t>
         </is>
       </c>
-      <c r="E4" s="3" t="inlineStr">
+      <c r="E4" s="4" t="inlineStr">
         <is>
           <t>Charging</t>
         </is>
       </c>
-      <c r="F4" s="3" t="inlineStr">
+      <c r="F4" s="4" t="inlineStr">
         <is>
           <t>Invoices</t>
         </is>
       </c>
-      <c r="G4" s="3" t="inlineStr">
+      <c r="G4" s="4" t="inlineStr">
         <is>
           <t>Boxes</t>
         </is>
       </c>
-      <c r="H4" s="3" t="inlineStr">
+      <c r="H4" s="4" t="inlineStr">
         <is>
           <t>Trip / box charge (owed to the auto)</t>
         </is>
       </c>
-      <c r="I4" s="3" t="inlineStr">
+      <c r="I4" s="4" t="inlineStr">
         <is>
           <t>Booked on the invoices (MIS)</t>
         </is>
       </c>
-      <c r="J4" s="3" t="inlineStr">
+      <c r="J4" s="4" t="inlineStr">
         <is>
           <t>Cost / box</t>
         </is>
       </c>
-      <c r="K4" s="3" t="inlineStr">
+      <c r="K4" s="4" t="inlineStr">
         <is>
           <t>Paid at dispatch</t>
         </is>
       </c>
-      <c r="L4" s="3" t="inlineStr">
+      <c r="L4" s="4" t="inlineStr">
         <is>
           <t>State</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="4" t="n">
+      <c r="A5" s="5" t="n">
         <v>46316</v>
       </c>
       <c r="B5" t="inlineStr">
@@ -569,22 +578,22 @@
           <t>Per trip</t>
         </is>
       </c>
-      <c r="F5" s="5" t="n">
+      <c r="F5" s="6" t="n">
         <v>4</v>
       </c>
-      <c r="G5" s="5" t="n">
+      <c r="G5" s="6" t="n">
         <v>30</v>
       </c>
-      <c r="H5" s="6" t="n">
+      <c r="H5" s="7" t="n">
         <v>500</v>
       </c>
-      <c r="I5" s="6" t="n">
+      <c r="I5" s="7" t="n">
         <v>500</v>
       </c>
-      <c r="J5" s="6" t="n">
+      <c r="J5" s="7" t="n">
         <v>16.67</v>
       </c>
-      <c r="K5" s="6" t="n">
+      <c r="K5" s="7" t="n">
         <v>500</v>
       </c>
       <c r="L5" t="inlineStr">
@@ -594,7 +603,7 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="4" t="n">
+      <c r="A6" s="5" t="n">
         <v>46316</v>
       </c>
       <c r="B6" t="inlineStr">
@@ -617,22 +626,22 @@
           <t>Per box</t>
         </is>
       </c>
-      <c r="F6" s="5" t="n">
+      <c r="F6" s="6" t="n">
         <v>2</v>
       </c>
-      <c r="G6" s="5" t="n">
+      <c r="G6" s="6" t="n">
         <v>21</v>
       </c>
-      <c r="H6" s="6" t="n">
+      <c r="H6" s="7" t="n">
         <v>432</v>
       </c>
-      <c r="I6" s="6" t="n">
+      <c r="I6" s="7" t="n">
         <v>432</v>
       </c>
-      <c r="J6" s="6" t="n">
+      <c r="J6" s="7" t="n">
         <v>20.57</v>
       </c>
-      <c r="K6" s="6" t="n">
+      <c r="K6" s="7" t="n">
         <v>432</v>
       </c>
       <c r="L6" t="inlineStr">
@@ -642,7 +651,7 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="4" t="n">
+      <c r="A7" s="5" t="n">
         <v>46316</v>
       </c>
       <c r="B7" t="inlineStr">
@@ -665,22 +674,22 @@
           <t>Per trip</t>
         </is>
       </c>
-      <c r="F7" s="5" t="n">
+      <c r="F7" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="G7" s="5" t="n">
+      <c r="G7" s="6" t="n">
         <v>10</v>
       </c>
-      <c r="H7" s="6" t="n">
+      <c r="H7" s="7" t="n">
         <v>550</v>
       </c>
-      <c r="I7" s="6" t="n">
+      <c r="I7" s="7" t="n">
         <v>550</v>
       </c>
-      <c r="J7" s="6" t="n">
+      <c r="J7" s="7" t="n">
         <v>55</v>
       </c>
-      <c r="K7" s="6" t="n">
+      <c r="K7" s="7" t="n">
         <v>550</v>
       </c>
       <c r="L7" t="inlineStr">
@@ -690,34 +699,34 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="7" t="inlineStr">
+      <c r="A8" s="8" t="inlineStr">
         <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="B8" s="8" t="n"/>
-      <c r="C8" s="8" t="n"/>
-      <c r="D8" s="8" t="n"/>
-      <c r="E8" s="8" t="n"/>
-      <c r="F8" s="9" t="n">
+      <c r="B8" s="9" t="n"/>
+      <c r="C8" s="9" t="n"/>
+      <c r="D8" s="9" t="n"/>
+      <c r="E8" s="9" t="n"/>
+      <c r="F8" s="10" t="n">
         <v>7</v>
       </c>
-      <c r="G8" s="9" t="n">
+      <c r="G8" s="10" t="n">
         <v>61</v>
       </c>
-      <c r="H8" s="10" t="n">
+      <c r="H8" s="11" t="n">
         <v>1482</v>
       </c>
-      <c r="I8" s="10" t="n">
+      <c r="I8" s="11" t="n">
         <v>1482</v>
       </c>
-      <c r="J8" s="10" t="n">
+      <c r="J8" s="11" t="n">
         <v>24.3</v>
       </c>
-      <c r="K8" s="10" t="n">
+      <c r="K8" s="11" t="n">
         <v>1482</v>
       </c>
-      <c r="L8" s="8" t="n"/>
+      <c r="L8" s="9" t="n"/>
     </row>
   </sheetData>
   <autoFilter ref="A4:L8"/>
